--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex001.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>数据状态</t>
   </si>
@@ -23,6 +23,9 @@
   </si>
   <si>
     <t>产品名称</t>
+  </si>
+  <si>
+    <t>产品主代码</t>
   </si>
   <si>
     <t>日期</t>
@@ -81,10 +84,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -102,6 +105,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -109,6 +134,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
@@ -124,21 +157,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
@@ -146,17 +164,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -168,24 +211,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -193,49 +220,25 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -248,19 +251,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -272,145 +419,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,12 +432,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -466,15 +469,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -486,6 +480,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -515,30 +542,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -547,10 +550,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -559,10 +562,10 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -571,129 +574,126 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1018,26 +1018,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.7545454545455" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1272727272727" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.9090909090909" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.0909090909091" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.2727272727273" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.5454545454545" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1272727272727" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="1" customWidth="1"/>
-    <col min="10" max="14" width="12.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5" style="1" customWidth="1"/>
-    <col min="16" max="17" width="12.8727272727273" style="1" customWidth="1"/>
-    <col min="18" max="18" width="23.7545454545455" style="1" customWidth="1"/>
-    <col min="19" max="20" width="8.72727272727273" style="1"/>
+    <col min="3" max="4" width="13.1272727272727" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.9090909090909" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.0909090909091" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.2727272727273" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5454545454545" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1272727272727" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" customWidth="1"/>
+    <col min="11" max="15" width="12.5" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5" style="1" customWidth="1"/>
+    <col min="17" max="18" width="12.8727272727273" style="1" customWidth="1"/>
+    <col min="19" max="19" width="23.7545454545455" style="1" customWidth="1"/>
+    <col min="20" max="21" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1047,16 +1047,16 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -1097,6 +1097,9 @@
       </c>
       <c r="T1" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D524E891-DE1E-42F2-A720-BB40060B8B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="30930" windowHeight="16890"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +27,6 @@
     <t>产品子代码</t>
   </si>
   <si>
-    <t>产品名称</t>
-  </si>
-  <si>
     <t>产品主代码</t>
   </si>
   <si>
@@ -83,12 +79,16 @@
   </si>
   <si>
     <t>更新人</t>
+  </si>
+  <si>
+    <t>产品全称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -410,27 +410,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="13.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.75" style="1" customWidth="1"/>
+    <col min="3" max="4" width="13.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="1" customWidth="1"/>
-    <col min="11" max="15" width="12.44140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.44140625" style="1" customWidth="1"/>
-    <col min="17" max="18" width="12.88671875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="23.77734375" style="1" customWidth="1"/>
-    <col min="20" max="21" width="8.77734375" style="1"/>
+    <col min="11" max="15" width="12.5" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5" style="1" customWidth="1"/>
+    <col min="17" max="18" width="12.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="23.75" style="1" customWidth="1"/>
+    <col min="20" max="21" width="8.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,61 +438,61 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/RepProdIndex001.xlsx
@@ -81,7 +81,7 @@
     <t>更新人</t>
   </si>
   <si>
-    <t>产品全称</t>
+    <t>子产品名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
